--- a/oradox_cleaned_real.xlsx
+++ b/oradox_cleaned_real.xlsx
@@ -15,15 +15,18 @@
     <sheet name="Cleaned_Product_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cleaned_Product_Master!$A$1:$AF$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cleaned_Product_Master!$A$1:$AF$17</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="226">
   <si>
     <t>Field</t>
   </si>
@@ -685,6 +688,45 @@
   </si>
   <si>
     <t>oradox-effervescent-periotabs.JPG</t>
+  </si>
+  <si>
+    <t>Mouthwash / Oral Rinse (Therapeutic dental rinse)</t>
+  </si>
+  <si>
+    <t>Concentrated oral care serum for enhanced gum and oral hygiene.</t>
+  </si>
+  <si>
+    <t>A potent oral serum formulated to support gum health, reduce bacteria, and provide long-lasting freshness. Ideal as an adjunct to daily oral hygiene routines.</t>
+  </si>
+  <si>
+    <t>Gum care and oral hygiene support.</t>
+  </si>
+  <si>
+    <t>Supports healthy gums</t>
+  </si>
+  <si>
+    <t>Liquid serum; 30 ml / 50 ml bottle; dropper or pump dispenser; concentrated formula</t>
+  </si>
+  <si>
+    <t>non sterile</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Store below 30°C, protect from heat and light</t>
+  </si>
+  <si>
+    <t>ORA-003</t>
+  </si>
+  <si>
+    <t>Oradox Oral Serum Fresh Flavor Mint, Orange, Lime, Strawberry</t>
+  </si>
+  <si>
+    <t>Oradox Oral Serum</t>
+  </si>
+  <si>
+    <t>Concentrated formula, antibacterial action, fresh flavor</t>
+  </si>
+  <si>
+    <t>Antibacterial agents, humectants, flavoring agents, aqueous base</t>
   </si>
 </sst>
 </file>
@@ -741,7 +783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -749,18 +791,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -771,6 +822,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,6 +865,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Chart1"/>
+      <sheetName val="Product_Master"/>
+      <sheetName val="Category_List"/>
+      <sheetName val="Instructions"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1084,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF16"/>
+  <dimension ref="A1:AF17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1114,1257 +1200,1351 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="30">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="30">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2" t="s">
+      <c r="S2" s="8"/>
+      <c r="T2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2" t="s">
+      <c r="U2" s="8"/>
+      <c r="V2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2" t="s">
+      <c r="W2" s="8"/>
+      <c r="X2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2" t="s">
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2" t="s">
+      <c r="AE2" s="8"/>
+      <c r="AF2" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="90">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2" t="s">
+      <c r="U3" s="8"/>
+      <c r="V3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2" t="s">
+      <c r="W3" s="8"/>
+      <c r="X3" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2" t="s">
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2" t="s">
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2" t="s">
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="45">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:32" ht="47.25" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="45">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="s">
+      <c r="S5" s="8"/>
+      <c r="T5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2" t="s">
+      <c r="U5" s="8"/>
+      <c r="V5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2" t="s">
+      <c r="W5" s="8"/>
+      <c r="X5" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2" t="s">
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2" t="s">
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="8"/>
+      <c r="AD5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2" t="s">
+      <c r="AE5" s="8"/>
+      <c r="AF5" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="60">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:32" ht="60">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E6" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I6" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J6" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K6" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L6" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O6" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="s">
+      <c r="S6" s="8"/>
+      <c r="T6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2" t="s">
+      <c r="U6" s="8"/>
+      <c r="V6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2" t="s">
+      <c r="W6" s="8"/>
+      <c r="X6" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2" t="s">
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2" t="s">
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2" t="s">
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="45">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:32" ht="45">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E7" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G7" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J7" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K7" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L7" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M7" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O7" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2" t="s">
+      <c r="S7" s="8"/>
+      <c r="T7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2" t="s">
+      <c r="U7" s="8"/>
+      <c r="V7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2" t="s">
+      <c r="W7" s="8"/>
+      <c r="X7" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2" t="s">
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2" t="s">
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2" t="s">
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="60">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:32" ht="60">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E8" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I8" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J8" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L8" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M8" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N8" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O8" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="s">
+      <c r="S8" s="8"/>
+      <c r="T8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2" t="s">
+      <c r="U8" s="8"/>
+      <c r="V8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2" t="s">
+      <c r="W8" s="8"/>
+      <c r="X8" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2" t="s">
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2" t="s">
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2" t="s">
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="45">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:32" ht="45">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E9" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I9" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K9" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L9" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M9" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N9" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O9" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="R9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="s">
+      <c r="S9" s="8"/>
+      <c r="T9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2" t="s">
+      <c r="U9" s="8"/>
+      <c r="V9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2" t="s">
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2" t="s">
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2" t="s">
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="60">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:32" ht="60">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E10" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G10" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I10" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J10" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K10" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L10" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="s">
+      <c r="S10" s="8"/>
+      <c r="T10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2" t="s">
+      <c r="U10" s="8"/>
+      <c r="V10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2" t="s">
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2" t="s">
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2" t="s">
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="45">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:32" ht="45">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E11" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G11" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I11" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J11" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K11" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L11" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M11" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N11" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O11" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="s">
+      <c r="S11" s="8"/>
+      <c r="T11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2" t="s">
+      <c r="U11" s="8"/>
+      <c r="V11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2" t="s">
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2" t="s">
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE10" s="2"/>
-      <c r="AF10" s="2" t="s">
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="45">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:32" ht="45">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E12" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I12" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J12" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="s">
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O12" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="R12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="s">
+      <c r="S12" s="8"/>
+      <c r="T12" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2" t="s">
+      <c r="U12" s="8"/>
+      <c r="V12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2" t="s">
+      <c r="W12" s="8"/>
+      <c r="X12" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2" t="s">
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2" t="s">
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2" t="s">
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="45">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+    <row r="13" spans="1:32" ht="45">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E13" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G13" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I13" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J13" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="s">
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O13" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="P13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="R13" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="s">
+      <c r="S13" s="8"/>
+      <c r="T13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2" t="s">
+      <c r="U13" s="8"/>
+      <c r="V13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2" t="s">
+      <c r="W13" s="8"/>
+      <c r="X13" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2" t="s">
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2" t="s">
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2" t="s">
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="45">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+    <row r="14" spans="1:32" ht="45">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E14" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F14" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G14" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I14" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J14" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="s">
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O14" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="P14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="Q14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="R14" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="s">
+      <c r="S14" s="8"/>
+      <c r="T14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2" t="s">
+      <c r="U14" s="8"/>
+      <c r="V14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2" t="s">
+      <c r="W14" s="8"/>
+      <c r="X14" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2" t="s">
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2" t="s">
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2" t="s">
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="60">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+    <row r="15" spans="1:32" ht="60">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G15" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H15" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I15" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J15" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="s">
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O15" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="P15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q15" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="s">
+      <c r="S15" s="8"/>
+      <c r="T15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2" t="s">
+      <c r="U15" s="8"/>
+      <c r="V15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2" t="s">
+      <c r="W15" s="8"/>
+      <c r="X15" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2" t="s">
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2" t="s">
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2" t="s">
+      <c r="AE15" s="8"/>
+      <c r="AF15" s="8" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="45">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:32" ht="45">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E16" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G16" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I16" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J16" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2" t="s">
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O16" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="P16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="R16" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2" t="s">
+      <c r="S16" s="8"/>
+      <c r="T16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2" t="s">
+      <c r="U16" s="8"/>
+      <c r="V16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2" t="s">
+      <c r="W16" s="8"/>
+      <c r="X16" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2" t="s">
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2" t="s">
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2" t="s">
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="45">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+    <row r="17" spans="1:32" ht="45">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E17" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G17" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I17" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J17" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="s">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O17" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="P17" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="Q17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="R17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2" t="s">
+      <c r="S17" s="8"/>
+      <c r="T17" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2" t="s">
+      <c r="U17" s="8"/>
+      <c r="V17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2" t="s">
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2" t="s">
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2" t="s">
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF16"/>
+  <autoFilter ref="A1:AF17"/>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'[oradoxxxxxxx (2).xlsx]Category_List'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>D4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'[oradoxxxxxxx (2).xlsx]Category_List'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>C4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2373,282 +2553,282 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>190</v>
       </c>
     </row>
